--- a/esyluban/examples/dev/DataTables/test/test_size.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_size.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -406,7 +406,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestSize" &amp; value_type="test.TestSize" &amp; read_schema_from_file="false" &amp; input="test/test_size.xlsx" &amp; output="test_tbtestsize"</t>
+          <t>full_name="test.TbTestSize" &amp; input="test/test_size.xlsx"</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
@@ -481,52 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
